--- a/ficheiros para milestone 2/userstoris.xlsx
+++ b/ficheiros para milestone 2/userstoris.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guiba\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\guiba\Desktop\LDS\ficheiros para milestone 2\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05A9D217-9B66-4C1E-B8AF-7088A714EFDD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{012C3CF4-DFFE-4104-8418-8A08C898FFB7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{982013A5-BAA1-47D2-B87C-A47FCA2ABBE8}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="97">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="158" uniqueCount="113">
   <si>
     <t>Descrição</t>
   </si>
@@ -156,19 +156,10 @@
     <t>US15: Remarcação de Consulta pelo Paciente</t>
   </si>
   <si>
-    <t>Como um Paciente, eu quero remarcar uma consulta confirmada para um novo horário disponível.</t>
-  </si>
-  <si>
     <t>US16: Lembrete de Consulta</t>
   </si>
   <si>
     <t>Como um Paciente , eu quero receber um lembrete (push notification) de uma consulta confirmada, para não me esquecer do compromisso.</t>
-  </si>
-  <si>
-    <t>US17: Notificação de Alteração/Cancelamento de Consulta</t>
-  </si>
-  <si>
-    <t>Como um Paciente ou Médico, eu quero ser notificado (push notification) quando uma consulta agendada é alterada ou cancelada pela outra parte, para estar ciente da mudança.</t>
   </si>
   <si>
     <t>Como um Paciente, eu quero ter um dashboard onde possa ver o meu histórico de consultas passadas e futuras.</t>
@@ -294,31 +285,14 @@
 - Frontend: Permitir que o utilizador clique num horário e passe por um fluxo de confirmação.</t>
   </si>
   <si>
-    <t>- Dado que um Paciente tem uma consulta "Confirmada", quando ele a cancela (respeitando o limite de antecedência), o estado da consulta muda para "Cancelada pelo Paciente" e o slot volta a ficar "Livre". O médico é notificado. 
-- Dado que um Médico tem uma consulta "Confirmada", quando ele a cancela, o estado da consulta muda para "Cancelada pelo Médico" e o slot volta a ficar "Livre". O paciente é notificado.</t>
-  </si>
-  <si>
     <t>- Backend: Criar um único endpoint POST /api/consultas/{id}/cancelar. A lógica de negócio no backend deve identificar quem fez o pedido. 
 - Frontend: O botão de cancelar deve estar disponível tanto no dashboard do Paciente como no do Médico.</t>
   </si>
   <si>
-    <t>- Dado que um Paciente tem uma consulta "Confirmada", quando ele solicita uma remarcação para um novo horário livre, a consulta é atualizada com a nova data/hora, o slot antigo é libertado e o novo é reservado. A remarcação deve seguir a mesma lógica de marcação imediata.</t>
-  </si>
-  <si>
-    <t>- Backend: Criar endpoint PUT /api/consultas/{id}/remarcar. A lógica deve verificar se o novo slot está livre e fazer a troca de forma atómica. 
-- Frontend: Implementar a interface de remarcação.</t>
-  </si>
-  <si>
     <t>- Dado que existe uma consulta confirmada agendada para as próximas 24 horas, o sistema verifica os agendamentos e é enviada um lembrete para o paciente.</t>
   </si>
   <si>
     <t>- Backend: Requer um serviço de agendamento de tarefas (scheduled job) que corre periodicamente.</t>
-  </si>
-  <si>
-    <t>- Dado que uma consulta confirmada é cancelada ou remarcada, quando a ação é concluída, uma notificação é enviada para o utilizador que não iniciou a ação.</t>
-  </si>
-  <si>
-    <t>- Backend: Acionar o envio da notificação nos endpoints de cancelamento e remarcação.</t>
   </si>
   <si>
     <t>- Dado que o Paciente acede ao seu dashboard, quando a página carrega, é exibida uma lista das suas consultas, ordenadas pela mais recente. O paciente pode inspecionar os detalhes de uma consulta.</t>
@@ -355,6 +329,95 @@
     <t>- Pré-requisito: O sistema precisa de uma forma de o Médico ou Admin marcar uma consulta como "Não Compareceu". Isto implica uma nova funcionalidade/estado na consulta. 
 - Backend: Criar endpoint para o relatório. 
 - Frontend-Web: Criar a interface de visualização.</t>
+  </si>
+  <si>
+    <t>Como Paciente, eu quero indicar na aplicação que vou chegar atrasado, para que os pacientes com consultas após a minha (no mesmo turno) sejam notificados antecipadamente.</t>
+  </si>
+  <si>
+    <t>- Backend: Implementar serviço de domínio para cálculo de turno e seleção de consultas subsequentes; garantir idempotência (ex.: chave única por consultaId + tipoEvento). 
+- Backend: Integrar com serviço de push notifications (fila/worker) e registo de auditoria. 
+- Frontend (Mobile/Web): Adicionar botão 'Chegarei atrasado' visível apenas antes da hora agendada; apresentar feedback de sucesso/erro. D16</t>
+  </si>
+  <si>
+    <t>Como Médico, eu quero indicar que vou chegar atrasado, para que o sistema procure um substituto disponível e notifique os pacientes afetados.</t>
+  </si>
+  <si>
+    <t>US23: Atraso do Médico e Substituição Automática</t>
+  </si>
+  <si>
+    <t>- Dado que o médico seleciona “Chegarei atrasado” antes da hora agendada, o sistema verifica se existe outro médico da mesma especialidade e horário disponível. 
+- Dado que é encontrado um substituto, o paciente é notificado e pode aceitar ou recusar a troca. - Dado que o paciente aceita a substituição, a consulta é atualizada para o novo médico. 
+- Dado que o paciente recusa ou não há substituto, a consulta mantém-se com o médico original.
+ - Dado que o médico assinala atraso, todos os pacientes seguintes no mesmo turno são notificados de um atraso de 30 minutos.</t>
+  </si>
+  <si>
+    <t>- Backend: Criar endpoint POST /api/consultas/{id}/atraso-medico que procura substituto, envia proposta ao paciente e notifica consultas seguintes.
+- Frontend: Adicionar botão “Chegarei atrasado” para médico e popup de aceitação/recusa para paciente. 
+- Notificações push enviadas aos pacientes seguintes no turno."</t>
+  </si>
+  <si>
+    <t>- Dado que um Paciente tem uma consulta "Reservada", quando ele a cancela (respeitando o limite de antecedência), o estado da consulta muda para "Cancelada" e o slot volta a ficar "Livre". O médico é notificado. 
+- Dado que um Médico tem uma consulta "Reservada", quando ele a cancela, (respeitando o limite de antecedência), o estado da consulta muda para "Cancelada" e o slot volta a ficar "Livre". O paciente é notificado.</t>
+  </si>
+  <si>
+    <t>- Dado que o paciente assinala “Chegarei atrasado”, quando existem outras consultas após a sua no mesmo turno (manhã/tarde), então apenas esses pacientes recebem uma notificação; consultas de outros turnos não são notificadas. 
+- Dado que o paciente tenta assinalar atraso após a hora agendada ou depois do fim do turno, então o sistema recusa a ação e apresenta mensagem adequada. 
+- Dado que já foi enviado um aviso de atraso para a mesma consulta, quando o paciente tenta repetir a ação, então o sistema não envia notificações duplicadas (idempotência). 
+- Dado que o processo de notificação é executado, quando concluído, então existe um registo/auditoria do evento (timestamp, utilizador, consultas notificadas)."</t>
+  </si>
+  <si>
+    <t>US17: Notificação de Cancelamento de Consulta</t>
+  </si>
+  <si>
+    <t>Como um Paciente ou Médico, eu quero ser notificado (push notification) quando uma consulta agendada é  cancelada pela outra parte, para estar ciente da mudança.</t>
+  </si>
+  <si>
+    <t>- Dado que uma consulta confirmada é cancelada, quando a ação é concluída, uma notificação é enviada para o utilizador que não iniciou a ação.</t>
+  </si>
+  <si>
+    <t>- Backend: Acionar o envio da notificação nos endpoints de cancelamento.</t>
+  </si>
+  <si>
+    <t>Como Médico, eu quero indicar que vou chegar atrasado, para que os pacientes seguintes no mesmo turno sejam notificados do atraso.</t>
+  </si>
+  <si>
+    <t>- Dado que o médico seleciona “Chegarei atrasado” antes da hora agendada, o sistema envia notificações push aos pacientes com consultas após a dele, informando um atraso de 30 minutos. 
+- Dado que o médico tenta assinalar atraso após a hora agendada, o sistema recusa o pedido. 
+- Dado que já foi enviada uma notificação de atraso para a mesma consulta, o sistema não envia duplicadas.</t>
+  </si>
+  <si>
+    <t>US24: Notificação de Atraso do Médico</t>
+  </si>
+  <si>
+    <t>- Backend: Criar endpoint POST /api/consultas/{id}/atraso-medico que identifica o turno e envia notificações push aos pacientes seguintes. 
+- Frontend: Botão “Chegarei atrasado” disponível apenas antes da hora marcada.</t>
+  </si>
+  <si>
+    <t>US25: Notificação de Atraso do Paciente</t>
+  </si>
+  <si>
+    <t>Como Paciente, eu quero indicar que vou chegar atrasado, para que o médico e os pacientes seguintes sejam avisados e possam ajustar os horários.</t>
+  </si>
+  <si>
+    <t>- Dado que o paciente seleciona “Chegarei atrasado” antes da hora agendada, o sistema envia notificações push aos pacientes seguintes no mesmo turno, informando que as consultas poderão começar 30 minutos mais cedo.
+ - Dado que o paciente tenta indicar atraso após a hora marcada, o sistema recusa a ação. 
+- Dado que já foi enviada uma notificação para a mesma consulta, o sistema não envia duplicadas.</t>
+  </si>
+  <si>
+    <t>- Backend: Criar endpoint POST /api/consultas/{id}/atraso-paciente que verifica o turno e envia notificações push ao médico e aos pacientes seguintes. 
+- Frontend: Adicionar botão “Chegarei atrasado” visível até à hora da consulta.</t>
+  </si>
+  <si>
+    <t>André</t>
+  </si>
+  <si>
+    <t>Diogo</t>
+  </si>
+  <si>
+    <t>Gonçalo</t>
+  </si>
+  <si>
+    <t>Guilherme</t>
   </si>
 </sst>
 </file>
@@ -498,7 +561,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
@@ -522,18 +585,26 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="13">
     <dxf>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color theme="0"/>
         </left>
-        <right/>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
         <top style="thin">
           <color theme="0"/>
         </top>
@@ -541,14 +612,12 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color theme="0"/>
         </left>
-        <right style="thin">
-          <color theme="0"/>
-        </right>
+        <right/>
         <top style="thin">
           <color theme="0"/>
         </top>
@@ -556,10 +625,7 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
-    <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color theme="0"/>
@@ -574,7 +640,7 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color theme="0"/>
@@ -589,7 +655,7 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color theme="0"/>
@@ -604,7 +670,7 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color theme="0"/>
@@ -619,7 +685,7 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left style="thin">
           <color theme="0"/>
@@ -634,7 +700,7 @@
       </border>
     </dxf>
     <dxf>
-      <alignment horizontal="left" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
       <border diagonalUp="0" diagonalDown="0" outline="0">
         <left/>
         <right style="thin">
@@ -644,6 +710,39 @@
           <color theme="0"/>
         </top>
         <bottom/>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color theme="0"/>
+        </left>
+        <right style="thin">
+          <color theme="0"/>
+        </right>
+        <top style="thin">
+          <color theme="0"/>
+        </top>
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color theme="0"/>
+        </bottom>
       </border>
     </dxf>
     <dxf>
@@ -662,36 +761,6 @@
         </right>
         <top/>
         <bottom/>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <top style="thin">
-          <color theme="0"/>
-        </top>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
-        <left style="thin">
-          <color theme="0"/>
-        </left>
-        <right style="thin">
-          <color theme="0"/>
-        </right>
-        <top style="thin">
-          <color theme="0"/>
-        </top>
-        <bottom style="thin">
-          <color theme="0"/>
-        </bottom>
       </border>
     </dxf>
   </dxfs>
@@ -708,17 +777,17 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F384CC1-0BC2-413A-9B25-E84D4B18D758}" name="Table1" displayName="Table1" ref="B3:I25" insertRowShift="1" totalsRowShown="0" headerRowDxfId="9" dataDxfId="2" headerRowBorderDxfId="11" tableBorderDxfId="12" totalsRowBorderDxfId="10">
-  <autoFilter ref="B3:I25" xr:uid="{1F384CC1-0BC2-413A-9B25-E84D4B18D758}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{1F384CC1-0BC2-413A-9B25-E84D4B18D758}" name="Table1" displayName="Table1" ref="B3:I28" insertRowShift="1" totalsRowShown="0" headerRowDxfId="12" dataDxfId="10" headerRowBorderDxfId="11" tableBorderDxfId="9" totalsRowBorderDxfId="8">
+  <autoFilter ref="B3:I28" xr:uid="{1F384CC1-0BC2-413A-9B25-E84D4B18D758}"/>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{920B1D59-6FD0-416D-9FF2-FEE9D0983694}" name="Título" dataDxfId="8"/>
-    <tableColumn id="2" xr3:uid="{680D0AC6-4CE8-48EF-BCFB-03948140A6E2}" name="Descrição" dataDxfId="7"/>
-    <tableColumn id="3" xr3:uid="{1647D1E5-9627-4862-9C3D-8691065746F2}" name="Critérios de Aceitação" dataDxfId="6"/>
-    <tableColumn id="8" xr3:uid="{4490F14B-200A-4E29-8874-01BE4153AF22}" name="Notas/Tarefas Técnicas" dataDxfId="5"/>
-    <tableColumn id="4" xr3:uid="{B4C3319D-1302-4ECA-AEFD-266A6692D8C3}" name="Prioridade" dataDxfId="4"/>
-    <tableColumn id="5" xr3:uid="{666559DA-E2DD-419E-8EBC-4F1F0933AB1E}" name="Story Points" dataDxfId="3"/>
-    <tableColumn id="6" xr3:uid="{E81AB74D-11A4-4854-A3CF-BD62490C1E4E}" name="Responsável" dataDxfId="1"/>
-    <tableColumn id="7" xr3:uid="{FC635F6F-64ED-4D11-942C-0774FC7A12AD}" name="Estado" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{920B1D59-6FD0-416D-9FF2-FEE9D0983694}" name="Título" dataDxfId="7"/>
+    <tableColumn id="2" xr3:uid="{680D0AC6-4CE8-48EF-BCFB-03948140A6E2}" name="Descrição" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{1647D1E5-9627-4862-9C3D-8691065746F2}" name="Critérios de Aceitação" dataDxfId="5"/>
+    <tableColumn id="8" xr3:uid="{4490F14B-200A-4E29-8874-01BE4153AF22}" name="Notas/Tarefas Técnicas" dataDxfId="4"/>
+    <tableColumn id="4" xr3:uid="{B4C3319D-1302-4ECA-AEFD-266A6692D8C3}" name="Prioridade" dataDxfId="3"/>
+    <tableColumn id="5" xr3:uid="{666559DA-E2DD-419E-8EBC-4F1F0933AB1E}" name="Story Points" dataDxfId="2"/>
+    <tableColumn id="6" xr3:uid="{E81AB74D-11A4-4854-A3CF-BD62490C1E4E}" name="Responsável" dataDxfId="0"/>
+    <tableColumn id="7" xr3:uid="{FC635F6F-64ED-4D11-942C-0774FC7A12AD}" name="Estado" dataDxfId="1"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1041,14 +1110,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AE6CC1C-EFAF-48DF-83E5-D6572C671D8C}">
-  <dimension ref="B3:I25"/>
+  <dimension ref="B3:I28"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="4.28515625" style="1" customWidth="1"/>
     <col min="2" max="2" width="32.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="35.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="29.85546875" style="1" customWidth="1"/>
     <col min="4" max="4" width="71.140625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="45.42578125" style="1" customWidth="1"/>
+    <col min="5" max="5" width="49" style="1" customWidth="1"/>
     <col min="6" max="6" width="12.42578125" style="1" customWidth="1"/>
     <col min="7" max="7" width="14" style="1" customWidth="1"/>
     <col min="8" max="8" width="14.7109375" style="1" customWidth="1"/>
@@ -1082,7 +1151,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="2:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="2:9" ht="90" x14ac:dyDescent="0.25">
       <c r="B4" s="6" t="s">
         <v>8</v>
       </c>
@@ -1093,16 +1162,18 @@
         <v>10</v>
       </c>
       <c r="E4" s="5" t="s">
-        <v>56</v>
+        <v>53</v>
       </c>
       <c r="F4" s="7"/>
       <c r="G4" s="7"/>
-      <c r="H4" s="7"/>
+      <c r="H4" s="11" t="s">
+        <v>109</v>
+      </c>
       <c r="I4" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="5" spans="2:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="2:9" ht="90" x14ac:dyDescent="0.25">
       <c r="B5" s="6" t="s">
         <v>12</v>
       </c>
@@ -1110,19 +1181,21 @@
         <v>13</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E5" s="9" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="F5" s="8"/>
       <c r="G5" s="8"/>
-      <c r="H5" s="8"/>
+      <c r="H5" s="12" t="s">
+        <v>110</v>
+      </c>
       <c r="I5" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="2:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="2:9" ht="75" x14ac:dyDescent="0.25">
       <c r="B6" s="6" t="s">
         <v>14</v>
       </c>
@@ -1130,19 +1203,21 @@
         <v>15</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="E6" s="9" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F6" s="8"/>
       <c r="G6" s="8"/>
-      <c r="H6" s="8"/>
+      <c r="H6" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="I6" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="7" spans="2:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="2:9" ht="75" x14ac:dyDescent="0.25">
       <c r="B7" s="6" t="s">
         <v>16</v>
       </c>
@@ -1150,19 +1225,21 @@
         <v>17</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="E7" s="9" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F7" s="8"/>
       <c r="G7" s="8"/>
-      <c r="H7" s="8"/>
+      <c r="H7" s="12" t="s">
+        <v>112</v>
+      </c>
       <c r="I7" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="8" spans="2:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="2:9" ht="105" x14ac:dyDescent="0.25">
       <c r="B8" s="6" t="s">
         <v>18</v>
       </c>
@@ -1170,19 +1247,21 @@
         <v>19</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="E8" s="9" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F8" s="8"/>
       <c r="G8" s="8"/>
-      <c r="H8" s="8"/>
+      <c r="H8" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="I8" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="9" spans="2:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="2:9" ht="90" x14ac:dyDescent="0.25">
       <c r="B9" s="6" t="s">
         <v>22</v>
       </c>
@@ -1190,19 +1269,21 @@
         <v>20</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="E9" s="9" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F9" s="8"/>
       <c r="G9" s="8"/>
-      <c r="H9" s="8"/>
+      <c r="H9" s="12" t="s">
+        <v>109</v>
+      </c>
       <c r="I9" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="2:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="2:9" ht="90" x14ac:dyDescent="0.25">
       <c r="B10" s="6" t="s">
         <v>21</v>
       </c>
@@ -1210,19 +1291,21 @@
         <v>23</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="E10" s="9" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F10" s="8"/>
       <c r="G10" s="8"/>
-      <c r="H10" s="8"/>
+      <c r="H10" s="12" t="s">
+        <v>110</v>
+      </c>
       <c r="I10" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="11" spans="2:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="2:9" ht="90" x14ac:dyDescent="0.25">
       <c r="B11" s="6" t="s">
         <v>24</v>
       </c>
@@ -1230,14 +1313,16 @@
         <v>25</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="E11" s="9" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F11" s="8"/>
       <c r="G11" s="8"/>
-      <c r="H11" s="8"/>
+      <c r="H11" s="12" t="s">
+        <v>112</v>
+      </c>
       <c r="I11" s="10" t="s">
         <v>11</v>
       </c>
@@ -1250,19 +1335,21 @@
         <v>27</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="E12" s="9" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F12" s="8"/>
       <c r="G12" s="8"/>
-      <c r="H12" s="8"/>
+      <c r="H12" s="12" t="s">
+        <v>110</v>
+      </c>
       <c r="I12" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="13" spans="2:9" ht="135" x14ac:dyDescent="0.25">
+    <row r="13" spans="2:9" ht="120" x14ac:dyDescent="0.25">
       <c r="B13" s="6" t="s">
         <v>28</v>
       </c>
@@ -1270,14 +1357,16 @@
         <v>29</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F13" s="8"/>
       <c r="G13" s="8"/>
-      <c r="H13" s="8"/>
+      <c r="H13" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="I13" s="10" t="s">
         <v>11</v>
       </c>
@@ -1290,14 +1379,16 @@
         <v>31</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="E14" s="9" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F14" s="8"/>
       <c r="G14" s="8"/>
-      <c r="H14" s="8"/>
+      <c r="H14" s="12" t="s">
+        <v>112</v>
+      </c>
       <c r="I14" s="10" t="s">
         <v>11</v>
       </c>
@@ -1310,14 +1401,16 @@
         <v>33</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="E15" s="5" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
+      <c r="H15" s="11" t="s">
+        <v>109</v>
+      </c>
       <c r="I15" s="10" t="s">
         <v>11</v>
       </c>
@@ -1330,19 +1423,21 @@
         <v>35</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="E16" s="9" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F16" s="8"/>
       <c r="G16" s="8"/>
-      <c r="H16" s="8"/>
+      <c r="H16" s="12" t="s">
+        <v>111</v>
+      </c>
       <c r="I16" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="17" spans="2:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="2:9" ht="90" x14ac:dyDescent="0.25">
       <c r="B17" s="6" t="s">
         <v>36</v>
       </c>
@@ -1350,175 +1445,259 @@
         <v>37</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>79</v>
+        <v>95</v>
       </c>
       <c r="E17" s="9" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="F17" s="8"/>
       <c r="G17" s="8"/>
-      <c r="H17" s="8"/>
+      <c r="H17" s="12" t="s">
+        <v>110</v>
+      </c>
       <c r="I17" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="2:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="2:9" ht="195" x14ac:dyDescent="0.25">
       <c r="B18" s="6" t="s">
         <v>38</v>
       </c>
       <c r="C18" s="8" t="s">
-        <v>39</v>
+        <v>89</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>81</v>
+        <v>96</v>
       </c>
       <c r="E18" s="9" t="s">
-        <v>82</v>
+        <v>90</v>
       </c>
       <c r="F18" s="8"/>
       <c r="G18" s="8"/>
-      <c r="H18" s="8"/>
+      <c r="H18" s="12" t="s">
+        <v>112</v>
+      </c>
       <c r="I18" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="19" spans="2:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="2:9" ht="75" x14ac:dyDescent="0.25">
       <c r="B19" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="C19" s="8" t="s">
         <v>40</v>
       </c>
-      <c r="C19" s="8" t="s">
-        <v>41</v>
-      </c>
       <c r="D19" s="9" t="s">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="E19" s="9" t="s">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="F19" s="8"/>
       <c r="G19" s="8"/>
-      <c r="H19" s="8"/>
+      <c r="H19" s="12" t="s">
+        <v>109</v>
+      </c>
       <c r="I19" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="20" spans="2:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="2:9" ht="90" x14ac:dyDescent="0.25">
       <c r="B20" s="6" t="s">
-        <v>42</v>
+        <v>97</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>43</v>
+        <v>98</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>85</v>
+        <v>99</v>
       </c>
       <c r="E20" s="9" t="s">
-        <v>86</v>
+        <v>100</v>
       </c>
       <c r="F20" s="8"/>
       <c r="G20" s="8"/>
-      <c r="H20" s="8"/>
+      <c r="H20" s="12" t="s">
+        <v>110</v>
+      </c>
       <c r="I20" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="21" spans="2:9" ht="99.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="2:9" ht="60" x14ac:dyDescent="0.25">
       <c r="B21" s="6" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E21" s="5" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="F21" s="7"/>
       <c r="G21" s="7"/>
-      <c r="H21" s="7"/>
+      <c r="H21" s="11" t="s">
+        <v>111</v>
+      </c>
       <c r="I21" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="22" spans="2:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="22" spans="2:9" ht="75" x14ac:dyDescent="0.25">
       <c r="B22" s="6" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="C22" s="8" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E22" s="9" t="s">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="F22" s="8"/>
       <c r="G22" s="8"/>
-      <c r="H22" s="8"/>
+      <c r="H22" s="12" t="s">
+        <v>109</v>
+      </c>
       <c r="I22" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="23" spans="2:9" ht="60" x14ac:dyDescent="0.25">
+    <row r="23" spans="2:9" ht="75" x14ac:dyDescent="0.25">
       <c r="B23" s="6" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="C23" s="8" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>91</v>
+        <v>83</v>
       </c>
       <c r="E23" s="9" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="F23" s="8"/>
       <c r="G23" s="8"/>
-      <c r="H23" s="8"/>
+      <c r="H23" s="12" t="s">
+        <v>112</v>
+      </c>
       <c r="I23" s="10" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="24" spans="2:9" ht="75" x14ac:dyDescent="0.25">
+    <row r="24" spans="2:9" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B24" s="6" t="s">
-        <v>52</v>
+        <v>49</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>93</v>
+        <v>85</v>
       </c>
       <c r="E24" s="5" t="s">
-        <v>94</v>
+        <v>86</v>
       </c>
       <c r="F24" s="7"/>
       <c r="G24" s="7"/>
-      <c r="H24" s="7"/>
+      <c r="H24" s="11" t="s">
+        <v>112</v>
+      </c>
       <c r="I24" s="10" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="25" spans="2:9" ht="90" x14ac:dyDescent="0.25">
       <c r="B25" s="6" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>95</v>
+        <v>87</v>
       </c>
       <c r="E25" s="5" t="s">
-        <v>96</v>
+        <v>88</v>
       </c>
       <c r="F25" s="7"/>
       <c r="G25" s="7"/>
-      <c r="H25" s="7"/>
+      <c r="H25" s="11" t="s">
+        <v>110</v>
+      </c>
       <c r="I25" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="26" spans="2:9" ht="150" x14ac:dyDescent="0.25">
+      <c r="B26" s="6" t="s">
+        <v>92</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>91</v>
+      </c>
+      <c r="D26" s="5" t="s">
+        <v>93</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>94</v>
+      </c>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="11" t="s">
+        <v>109</v>
+      </c>
+      <c r="I26" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="27" spans="2:9" ht="105" x14ac:dyDescent="0.25">
+      <c r="B27" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D27" s="5" t="s">
+        <v>102</v>
+      </c>
+      <c r="E27" s="5" t="s">
+        <v>104</v>
+      </c>
+      <c r="F27" s="7"/>
+      <c r="G27" s="7"/>
+      <c r="H27" s="11" t="s">
+        <v>111</v>
+      </c>
+      <c r="I27" s="10" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="28" spans="2:9" ht="120" x14ac:dyDescent="0.25">
+      <c r="B28" s="6" t="s">
+        <v>105</v>
+      </c>
+      <c r="C28" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D28" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E28" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F28" s="7"/>
+      <c r="G28" s="7"/>
+      <c r="H28" s="11" t="s">
+        <v>110</v>
+      </c>
+      <c r="I28" s="10" t="s">
         <v>11</v>
       </c>
     </row>
